--- a/2adults-1days-chart.xlsx
+++ b/2adults-1days-chart.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="21">
   <si>
     <t>Отели</t>
   </si>
@@ -69,7 +69,13 @@
     <t>Выборка</t>
   </si>
   <si>
-    <t>13.09.2021</t>
+    <t>22.09.2021</t>
+  </si>
+  <si>
+    <t>23.09.2021</t>
+  </si>
+  <si>
+    <t>24.09.2021</t>
   </si>
   <si>
     <t>Рынок без KK и Лейкари</t>
@@ -1220,7 +1226,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1281,31 +1287,31 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>50</v>
       </c>
       <c r="D2">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E2">
         <v>86</v>
       </c>
       <c r="F2">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H2">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>260</v>
+        <v>62</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -1320,13 +1326,119 @@
         <v>49</v>
       </c>
       <c r="O2">
+        <v>59</v>
+      </c>
+      <c r="P2">
+        <v>61</v>
+      </c>
+      <c r="Q2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>45</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+      <c r="D3">
+        <v>59</v>
+      </c>
+      <c r="E3">
+        <v>129</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>67</v>
+      </c>
+      <c r="H3">
+        <v>66</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>62</v>
+      </c>
+      <c r="K3">
+        <v>88</v>
+      </c>
+      <c r="L3">
+        <v>87</v>
+      </c>
+      <c r="M3">
+        <v>99</v>
+      </c>
+      <c r="N3">
+        <v>49</v>
+      </c>
+      <c r="O3">
         <v>69</v>
       </c>
-      <c r="P2">
-        <v>91</v>
-      </c>
-      <c r="Q2">
+      <c r="P3">
+        <v>69</v>
+      </c>
+      <c r="Q3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>49</v>
+      </c>
+      <c r="C4">
+        <v>51</v>
+      </c>
+      <c r="D4">
         <v>0</v>
+      </c>
+      <c r="E4">
+        <v>97</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>81</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>94</v>
+      </c>
+      <c r="M4">
+        <v>99</v>
+      </c>
+      <c r="N4">
+        <v>49</v>
+      </c>
+      <c r="O4">
+        <v>89</v>
+      </c>
+      <c r="P4">
+        <v>70</v>
+      </c>
+      <c r="Q4">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1351,7 +1463,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1365,7 +1477,7 @@
         <v>15</v>
       </c>
       <c r="D1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1" t="s">
         <v>16</v>
@@ -1379,13 +1491,47 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>31</v>
+      </c>
+      <c r="C3">
+        <v>42</v>
+      </c>
+      <c r="D3">
+        <v>51</v>
+      </c>
+      <c r="E3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4">
+        <v>77</v>
+      </c>
+      <c r="C4">
+        <v>72</v>
+      </c>
+      <c r="D4">
+        <v>79</v>
+      </c>
+      <c r="E4">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
